--- a/docs/2/os/Учебный_план_Операционные_системы_и_среды.xlsx
+++ b/docs/2/os/Учебный_план_Операционные_системы_и_среды.xlsx
@@ -174,7 +174,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="45" customHeight="1">
+    <row r="6" ht="60" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
@@ -195,16 +195,16 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Операционная система: назначение и место в ИС»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Операционная система распределяет процессор, память и устройства между программами. Разберём её место в информационной системе и границу между ядром и приложениями.</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Операционная система: назначение и место в ИС</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="45" customHeight="1">
+          <t xml:space="preserve">ядро, оболочка, системный вызов, разделение ресурсов, прикладная программа</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="60" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
@@ -225,16 +225,16 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Архитектура ОС: ядро, драйверы, пользовательское пространство»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Ядро работает в привилегированном режиме, а приложения обращаются к железу только через системные вызовы. Разберём слои ОС, драйверы и цену переключения режимов.</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Архитектура ОС: ядро, драйверы, пользовательское пространство</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="45" customHeight="1">
+          <t xml:space="preserve">ядро, микроядро, драйвер, системный вызов, режим ядра, модуль</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">3-4</t>
@@ -255,16 +255,16 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Установка VirtualBox и создание виртуальной машины; Установка Linux в VirtualBox.</t>
+          <t xml:space="preserve">Создаёте виртуальную машину в VirtualBox, ставите Linux и настраиваете сеть и общие папки. Сдаёте отчёт со скриншотами установки и проверкой загрузки системы.</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Установка VirtualBox и создание виртуальной машины, Установка Linux в VirtualBox</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="45" customHeight="1">
+          <t xml:space="preserve">VirtualBox, виртуальный диск, ISO-образ, установка Linux, сетевой адаптер</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
@@ -285,16 +285,16 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Процессы и потоки»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Процесс владеет адресным пространством, а потоки делят его между собой. Разберём состояния процесса, переключение контекста и разницу между процессом и потоком.</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Процессы и потоки</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="45" customHeight="1">
+          <t xml:space="preserve">процесс, поток, состояние процесса, переключение контекста, PCB</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="60" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
@@ -315,12 +315,12 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Установка Windows 10 в VirtualBox»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Ставите Windows 10 во вторую виртуальную машину, разбиваете диск и завершаете первичную настройку. Сдаёте отчёт с параметрами машины и скриншотами ключевых шагов.</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Установка Windows 10 в VirtualBox</t>
+          <t xml:space="preserve">Windows 10, разметка диска, установка, драйверы, учётная запись</t>
         </is>
       </c>
     </row>
@@ -345,12 +345,12 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Планирование процессов»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Планировщик выбирает, какой готовый процесс получит процессор и на сколько. Сравним FCFS, SJF и круговой алгоритм по времени ожидания и реакции.</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Планирование процессов</t>
+          <t xml:space="preserve">планировщик, квант времени, очередь готовых, FCFS, круговая очередь, приоритет</t>
         </is>
       </c>
     </row>
@@ -375,12 +375,12 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Работа с командной строкой Linux»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Работаете в терминале Linux: навигация по каталогам, файлы, поиск и конвейеры. Сдаёте протокол команд с результатами и разбором трёх конвейеров.</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Работа с командной строкой Linux</t>
+          <t xml:space="preserve">терминал, конвейер, перенаправление, grep, права на файл</t>
         </is>
       </c>
     </row>
@@ -405,16 +405,16 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Синхронизация и взаимные блокировки»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Общий ресурс без синхронизации даёт гонки, а неверный порядок захвата приводит к взаимной блокировке. Разберём мьютексы, семафоры и условия тупика.</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Синхронизация и взаимные блокировки</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="45" customHeight="1">
+          <t xml:space="preserve">критическая секция, мьютекс, семафор, гонка данных, тупик, порядок захвата</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="60" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">10</t>
@@ -435,16 +435,16 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Управление памятью и виртуальная память»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Виртуальные адреса скрывают от программы физическую память и позволяют работать с объёмом больше доступного. Разберём страницы, таблицу страниц и подкачку.</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Управление памятью и виртуальная память</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="45" customHeight="1">
+          <t xml:space="preserve">виртуальная память, страница, таблица страниц, подкачка, своп, фрагментация</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="60" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">11-12</t>
@@ -465,16 +465,16 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Файлы, каталоги и права в Linux; Пользователи и группы в Linux.</t>
+          <t xml:space="preserve">Создаёте структуру каталогов, назначаете права и владельцев, заводите пользователей и группы. Сдаёте отчёт с деревом каталогов, таблицей прав и проверкой доступа.</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Файлы, каталоги и права в Linux, Пользователи и группы в Linux</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="45" customHeight="1">
+          <t xml:space="preserve">chmod, владелец файла, группа, umask, домашний каталог</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="60" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">13</t>
@@ -495,16 +495,16 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Файловые системы»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Файловая система хранит не только данные, но и метаданные: имена, права, блоки. Сравним ext4, NTFS и FAT по журналированию, надёжности и ограничениям.</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Файловые системы</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="45" customHeight="1">
+          <t xml:space="preserve">inode, блок, журналирование, ext4, NTFS, монтирование</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="60" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">14</t>
@@ -525,12 +525,12 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Процессы и управление ими»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Запускаете, останавливаете и переводите в фон процессы Linux, смотрите их состояние и завершаете зависшие. Сдаёте протокол с выводом ps, top и описанием действий.</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Процессы и управление ими</t>
+          <t xml:space="preserve">ps, top, kill, фоновый процесс, PID, сигнал</t>
         </is>
       </c>
     </row>
@@ -555,16 +555,16 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Ввод-вывод и драйверы устройств»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Устройство общается с процессором через контроллер, прерывания и буферы. Разберём опрос, прерывания и DMA, а также роль драйвера в этой цепочке.</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ввод-вывод и драйверы устройств</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="45" customHeight="1">
+          <t xml:space="preserve">прерывание, DMA, буферизация, контроллер устройства, драйвер, опрос</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="60" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">16</t>
@@ -585,16 +585,16 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Сценарии Bash»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Пишете сценарий Bash с аргументами, условиями и циклом, который автоматизирует обслуживание каталога. Сдаёте скрипт с комментариями и журналом запуска.</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сценарии Bash</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="45" customHeight="1">
+          <t xml:space="preserve">shebang, переменная, условие, цикл, код возврата</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="60" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">17</t>
@@ -615,16 +615,16 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Пользователи, права и безопасность ОС»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Доступ строится на учётных записях, группах и правах, а защита включает политики паролей и минимальные привилегии. Разберём модели доступа Linux и Windows.</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Пользователи, права и безопасность ОС</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="45" customHeight="1">
+          <t xml:space="preserve">аутентификация, авторизация, минимальные привилегии, sudo, политика паролей</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="60" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">18</t>
@@ -645,16 +645,16 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Командная строка и сценарии администрирования»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Администратор автоматизирует повторяющиеся операции командной строкой и сценариями. Разберём разницу подходов Linux и Windows и когда сценарий лучше ручной работы.</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Командная строка и сценарии администрирования</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="45" customHeight="1">
+          <t xml:space="preserve">оболочка, PowerShell, Bash, параметры команды, автоматизация</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="60" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">19-20</t>
@@ -675,16 +675,16 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Работа с командной строкой Windows; Права доступа и общие папки Windows.</t>
+          <t xml:space="preserve">Работаете в командной строке Windows, затем настраиваете общий каталог и права NTFS для группы. Сдаёте отчёт с командами, списком разрешений и проверкой доступа.</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Работа с командной строкой Windows, Права доступа и общие папки Windows</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="45" customHeight="1">
+          <t xml:space="preserve">cmd, icacls, общий ресурс, разрешения NTFS, сетевая папка</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="60" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">21</t>
@@ -705,16 +705,16 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Службы и автозагрузка»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Служба запускается без входа пользователя и работает в фоне по расписанию или событию. Разберём типы запуска, зависимости и точки автозагрузки в Linux и Windows.</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Службы и автозагрузка</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="45" customHeight="1">
+          <t xml:space="preserve">systemd, демон, тип запуска, зависимости службы, автозагрузка</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="60" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">22</t>
@@ -735,12 +735,12 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Службы и планировщик Windows»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Создаёте службу и задание в планировщике Windows, проверяете запуск по расписанию и по событию. Сдаёте отчёт с настройками, журналом и разбором сбоя.</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Службы и планировщик Windows</t>
+          <t xml:space="preserve">sc.exe, планировщик заданий, триггер, учётная запись службы, журнал</t>
         </is>
       </c>
     </row>
@@ -765,12 +765,12 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Виртуализация: VirtualBox, Linux и Windows 10»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Гипервизор делит ресурсы хоста между гостевыми системами, а его тип определяет скорость и изоляцию. Разберём режимы сети VirtualBox и общие папки.</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Виртуализация: VirtualBox, Linux и Windows 10</t>
+          <t xml:space="preserve">гипервизор, гостевая система, NAT, сетевой мост, снимок</t>
         </is>
       </c>
     </row>
@@ -795,16 +795,16 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Диагностика сети в ОС»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Проверяете сеть виртуальной машины по шагам: адрес, шлюз, DNS и доступность узла. Сдаёте протокол диагностики с найденной причиной сбоя.</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Диагностика сети в ОС</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="45" customHeight="1">
+          <t xml:space="preserve">ip-адрес, шлюз, DNS, ping, traceroute</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="60" customHeight="1">
       <c r="A27" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">25</t>
@@ -825,12 +825,12 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Диагностика, журналы и восстановление ОС»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Сбой оставляет следы в журналах, а восстановление начинается с резервной копии и точки возврата. Разберём порядок диагностики от симптома к причине.</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Диагностика, журналы и восстановление ОС</t>
+          <t xml:space="preserve">журнал событий, уровень сообщения, точка восстановления, загрузочный образ, резервная копия</t>
         </is>
       </c>
     </row>
@@ -855,16 +855,16 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Журналы событий и поиск ошибок»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Ищете причину сбоя по журналам Linux и Windows: фильтруете события, сопоставляете время и находите первую ошибку. Сдаёте разбор с цепочкой событий.</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Журналы событий и поиск ошибок</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="45" customHeight="1">
+          <t xml:space="preserve">journalctl, просмотр событий, фильтр, идентификатор события, время сбоя</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="60" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">27-28</t>
@@ -885,12 +885,12 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Управление пакетами Linux; Диски, разделы и файловые системы.</t>
+          <t xml:space="preserve">Ставите и удаляете пакеты, затем размечаете новый диск, создаёте файловую систему и монтируете её. Сдаёте отчёт с командами, выводом и записью в fstab.</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Управление пакетами Linux, Диски, разделы и файловые системы</t>
+          <t xml:space="preserve">apt, раздел, mkfs, mount, fstab</t>
         </is>
       </c>
     </row>
@@ -915,16 +915,16 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Монтирование и общие папки VirtualBox»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Подключаете общую папку хоста в гостевую систему и проверяете права доступа к ней. Сдаёте отчёт с командами монтирования и проверкой обмена файлами.</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Монтирование и общие папки VirtualBox</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="45" customHeight="1">
+          <t xml:space="preserve">общая папка, монтирование, vboxsf, права доступа, гостевая система</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="60" customHeight="1">
       <c r="A31" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">30-31</t>
@@ -945,16 +945,16 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Снимки и клонирование виртуальных машин; Резервное копирование и восстановление.</t>
+          <t xml:space="preserve">Делаете снимки виртуальной машины, клонируете её и восстанавливаете состояние после намеренной поломки. Сдаёте отчёт с деревом снимков и проверкой восстановления.</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Снимки и клонирование виртуальных машин, Резервное копирование и восстановление</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="45" customHeight="1">
+          <t xml:space="preserve">снимок, клон, дифференциальный диск, восстановление, резервная копия</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="60" customHeight="1">
       <c r="A32" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">32-33</t>
@@ -975,16 +975,16 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Политики безопасности ОС; Аудит и мониторинг ОС.</t>
+          <t xml:space="preserve">Настраиваете политику паролей и аудит входа, затем проверяете события мониторинга. Сдаёте отчёт с настройками, событиями аудита и выводами по рискам.</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Политики безопасности ОС, Аудит и мониторинг ОС</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="45" customHeight="1">
+          <t xml:space="preserve">политика паролей, аудит, блокировка учётной записи, мониторинг, событие входа</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="60" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">34</t>
@@ -1005,16 +1005,16 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Сравнение Linux и Windows по администрированию»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Сравниваете две системы по десяти задачам администрирования и сводите результат в таблицу с командами и выводами. Сдаёте таблицу и вывод о выборе системы.</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сравнение Linux и Windows по администрированию</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="45" customHeight="1">
+          <t xml:space="preserve">сравнение, команды администрирования, права, службы, журналы</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="60" customHeight="1">
       <c r="A34" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">35</t>
@@ -1035,12 +1035,12 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Итоговая работа: настройка виртуального стенда»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Собираете стенд из двух виртуальных машин с сетью, общими папками и резервной копией. Сдаёте работающий стенд и отчёт с проверкой каждого требования.</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Итоговая работа: настройка виртуального стенда</t>
+          <t xml:space="preserve">виртуальный стенд, сеть машин, чек-лист, резервная копия, отчёт</t>
         </is>
       </c>
     </row>

--- a/docs/2/os/Учебный_план_Операционные_системы_и_среды.xlsx
+++ b/docs/2/os/Учебный_план_Операционные_системы_и_среды.xlsx
@@ -160,7 +160,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Минуты</t>
+          <t xml:space="preserve">Часы</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -191,7 +191,7 @@
         </is>
       </c>
       <c r="D6" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
@@ -221,7 +221,7 @@
         </is>
       </c>
       <c r="D7" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
@@ -251,7 +251,7 @@
         </is>
       </c>
       <c r="D8" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
@@ -281,7 +281,7 @@
         </is>
       </c>
       <c r="D9" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
@@ -311,7 +311,7 @@
         </is>
       </c>
       <c r="D10" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
@@ -341,7 +341,7 @@
         </is>
       </c>
       <c r="D11" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
@@ -371,7 +371,7 @@
         </is>
       </c>
       <c r="D12" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
@@ -401,7 +401,7 @@
         </is>
       </c>
       <c r="D13" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
@@ -431,7 +431,7 @@
         </is>
       </c>
       <c r="D14" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
@@ -461,7 +461,7 @@
         </is>
       </c>
       <c r="D15" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="D16" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="D17" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="D18" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="D19" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="D20" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="D21" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="D22" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="D23" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="D24" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="D25" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="D26" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="D27" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="D28" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="D29" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="D30" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="D31" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="D32" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="D33" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="D34" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="D35" s="6">
-        <v>3150</v>
+        <v>70</v>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>

--- a/docs/2/os/Учебный_план_Операционные_системы_и_среды.xlsx
+++ b/docs/2/os/Учебный_план_Операционные_системы_и_среды.xlsx
@@ -237,189 +237,189 @@
     <row r="8" ht="60" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">3-4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 1. Установка VirtualBox и создание виртуальной машины; Установка Linux в VirtualBox</t>
+          <t xml:space="preserve">Лекция 3. Процессы и потоки</t>
         </is>
       </c>
       <c r="D8" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Создаёте виртуальную машину в VirtualBox, ставите Linux и настраиваете сеть и общие папки. Сдаёте отчёт со скриншотами установки и проверкой загрузки системы.</t>
+          <t xml:space="preserve">Процесс владеет адресным пространством, а потоки делят его между собой. Разберём состояния процесса, переключение контекста и разницу между процессом и потоком.</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">VirtualBox, виртуальный диск, ISO-образ, установка Linux, сетевой адаптер</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="60" customHeight="1">
+          <t xml:space="preserve">процесс, поток, состояние процесса, переключение контекста, PCB</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="45" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Лекция</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Лекция 4. Планирование процессов</t>
+        </is>
+      </c>
+      <c r="D9" s="6">
+        <v>2</v>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Планировщик выбирает, какой готовый процесс получит процессор и на сколько. Сравним FCFS, SJF и круговой алгоритм по времени ожидания и реакции.</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">планировщик, квант времени, очередь готовых, FCFS, круговая очередь, приоритет</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="45" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Лекция</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Лекция 3. Процессы и потоки</t>
-        </is>
-      </c>
-      <c r="D9" s="6">
-        <v>2</v>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Процесс владеет адресным пространством, а потоки делят его между собой. Разберём состояния процесса, переключение контекста и разницу между процессом и потоком.</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">процесс, поток, состояние процесса, переключение контекста, PCB</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Лекция</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Лекция 5. Синхронизация и взаимные блокировки</t>
+        </is>
+      </c>
+      <c r="D10" s="6">
+        <v>2</v>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Общий ресурс без синхронизации даёт гонки, а неверный порядок захвата приводит к взаимной блокировке. Разберём мьютексы, семафоры и условия тупика.</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">критическая секция, мьютекс, семафор, гонка данных, тупик, порядок захвата</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Практика</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Практика 2. Установка Windows 10 в VirtualBox</t>
-        </is>
-      </c>
-      <c r="D10" s="6">
-        <v>2</v>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ставите Windows 10 во вторую виртуальную машину, разбиваете диск и завершаете первичную настройку. Сдаёте отчёт с параметрами машины и скриншотами ключевых шагов.</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Windows 10, разметка диска, установка, драйверы, учётная запись</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="45" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Практика</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Практика 1. Процессы и управление ими</t>
+        </is>
+      </c>
+      <c r="D11" s="6">
+        <v>2</v>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Запускаете, останавливаете и переводите в фон процессы Linux, смотрите их состояние и завершаете зависшие. Сдаёте протокол с выводом ps, top и описанием действий.</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ps, top, kill, фоновый процесс, PID, сигнал</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Лекция</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Лекция 4. Планирование процессов</t>
-        </is>
-      </c>
-      <c r="D11" s="6">
-        <v>2</v>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Планировщик выбирает, какой готовый процесс получит процессор и на сколько. Сравним FCFS, SJF и круговой алгоритм по времени ожидания и реакции.</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">планировщик, квант времени, очередь готовых, FCFS, круговая очередь, приоритет</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="45" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Лекция</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Лекция 6. Управление памятью и виртуальная память</t>
+        </is>
+      </c>
+      <c r="D12" s="6">
+        <v>2</v>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Виртуальные адреса скрывают от программы физическую память и позволяют работать с объёмом больше доступного. Разберём страницы, таблицу страниц и подкачку.</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">виртуальная память, страница, таблица страниц, подкачка, своп, фрагментация</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Практика</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Практика 3. Работа с командной строкой Linux</t>
-        </is>
-      </c>
-      <c r="D12" s="6">
-        <v>2</v>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Работаете в терминале Linux: навигация по каталогам, файлы, поиск и конвейеры. Сдаёте протокол команд с результатами и разбором трёх конвейеров.</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">терминал, конвейер, перенаправление, grep, права на файл</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="45" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Лекция</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Лекция 7. Файловые системы</t>
+        </is>
+      </c>
+      <c r="D13" s="6">
+        <v>2</v>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Файловая система хранит не только данные, но и метаданные: имена, права, блоки. Сравним ext4, NTFS и FAT по журналированию, надёжности и ограничениям.</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inode, блок, журналирование, ext4, NTFS, монтирование</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="45" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">9</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Лекция</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Лекция 5. Синхронизация и взаимные блокировки</t>
-        </is>
-      </c>
-      <c r="D13" s="6">
-        <v>2</v>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Общий ресурс без синхронизации даёт гонки, а неверный порядок захвата приводит к взаимной блокировке. Разберём мьютексы, семафоры и условия тупика.</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">критическая секция, мьютекс, семафор, гонка данных, тупик, порядок захвата</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10</t>
-        </is>
-      </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Лекция</t>
@@ -427,7 +427,7 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 6. Управление памятью и виртуальная память</t>
+          <t xml:space="preserve">Лекция 8. Ввод-вывод и драйверы устройств</t>
         </is>
       </c>
       <c r="D14" s="6">
@@ -435,89 +435,89 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Виртуальные адреса скрывают от программы физическую память и позволяют работать с объёмом больше доступного. Разберём страницы, таблицу страниц и подкачку.</t>
+          <t xml:space="preserve">Устройство общается с процессором через контроллер, прерывания и буферы. Разберём опрос, прерывания и DMA, а также роль драйвера в этой цепочке.</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">виртуальная память, страница, таблица страниц, подкачка, своп, фрагментация</t>
+          <t xml:space="preserve">прерывание, DMA, буферизация, контроллер устройства, драйвер, опрос</t>
         </is>
       </c>
     </row>
     <row r="15" ht="60" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">11-12</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 4. Файлы, каталоги и права в Linux; Пользователи и группы в Linux</t>
+          <t xml:space="preserve">Лекция 9. Пользователи, права и безопасность ОС</t>
         </is>
       </c>
       <c r="D15" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Создаёте структуру каталогов, назначаете права и владельцев, заводите пользователей и группы. Сдаёте отчёт с деревом каталогов, таблицей прав и проверкой доступа.</t>
+          <t xml:space="preserve">Доступ строится на учётных записях, группах и правах, а защита включает политики паролей и минимальные привилегии. Разберём модели доступа Linux и Windows.</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">chmod, владелец файла, группа, umask, домашний каталог</t>
+          <t xml:space="preserve">аутентификация, авторизация, минимальные привилегии, sudo, политика паролей</t>
         </is>
       </c>
     </row>
     <row r="16" ht="60" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">11-12</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 7. Файловые системы</t>
+          <t xml:space="preserve">Практика 2. Файлы, каталоги и права в Linux; Пользователи и группы в Linux</t>
         </is>
       </c>
       <c r="D16" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Файловая система хранит не только данные, но и метаданные: имена, права, блоки. Сравним ext4, NTFS и FAT по журналированию, надёжности и ограничениям.</t>
+          <t xml:space="preserve">Создаёте структуру каталогов, назначаете права и владельцев, заводите пользователей и группы. Сдаёте отчёт с деревом каталогов, таблицей прав и проверкой доступа.</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">inode, блок, журналирование, ext4, NTFS, монтирование</t>
+          <t xml:space="preserve">chmod, владелец файла, группа, umask, домашний каталог</t>
         </is>
       </c>
     </row>
     <row r="17" ht="60" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 5. Процессы и управление ими</t>
+          <t xml:space="preserve">Лекция 10. Командная строка и сценарии администрирования</t>
         </is>
       </c>
       <c r="D17" s="6">
@@ -525,29 +525,29 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Запускаете, останавливаете и переводите в фон процессы Linux, смотрите их состояние и завершаете зависшие. Сдаёте протокол с выводом ps, top и описанием действий.</t>
+          <t xml:space="preserve">Администратор автоматизирует повторяющиеся операции командной строкой и сценариями. Разберём разницу подходов Linux и Windows и когда сценарий лучше ручной работы.</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ps, top, kill, фоновый процесс, PID, сигнал</t>
+          <t xml:space="preserve">оболочка, PowerShell, Bash, параметры команды, автоматизация</t>
         </is>
       </c>
     </row>
     <row r="18" ht="45" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 8. Ввод-вывод и драйверы устройств</t>
+          <t xml:space="preserve">Практика 3. Работа с командной строкой Linux</t>
         </is>
       </c>
       <c r="D18" s="6">
@@ -555,19 +555,19 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Устройство общается с процессором через контроллер, прерывания и буферы. Разберём опрос, прерывания и DMA, а также роль драйвера в этой цепочке.</t>
+          <t xml:space="preserve">Работаете в терминале Linux: навигация по каталогам, файлы, поиск и конвейеры. Сдаёте протокол команд с результатами и разбором трёх конвейеров.</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">прерывание, DMA, буферизация, контроллер устройства, драйвер, опрос</t>
+          <t xml:space="preserve">терминал, конвейер, перенаправление, grep, права на файл</t>
         </is>
       </c>
     </row>
     <row r="19" ht="60" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
@@ -577,7 +577,7 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 6. Сценарии Bash</t>
+          <t xml:space="preserve">Практика 4. Сценарии Bash</t>
         </is>
       </c>
       <c r="D19" s="6">
@@ -597,90 +597,90 @@
     <row r="20" ht="60" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">16-17</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 9. Пользователи, права и безопасность ОС</t>
+          <t xml:space="preserve">Практика 5. Работа с командной строкой Windows; Права доступа и общие папки Windows</t>
         </is>
       </c>
       <c r="D20" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Доступ строится на учётных записях, группах и правах, а защита включает политики паролей и минимальные привилегии. Разберём модели доступа Linux и Windows.</t>
+          <t xml:space="preserve">Работаете в командной строке Windows, затем настраиваете общий каталог и права NTFS для группы. Сдаёте отчёт с командами, списком разрешений и проверкой доступа.</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">аутентификация, авторизация, минимальные привилегии, sudo, политика паролей</t>
+          <t xml:space="preserve">cmd, icacls, общий ресурс, разрешения NTFS, сетевая папка</t>
         </is>
       </c>
     </row>
     <row r="21" ht="60" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">18-19</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 10. Командная строка и сценарии администрирования</t>
+          <t xml:space="preserve">Практика 6. Управление пакетами Linux; Диски, разделы и файловые системы</t>
         </is>
       </c>
       <c r="D21" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Администратор автоматизирует повторяющиеся операции командной строкой и сценариями. Разберём разницу подходов Linux и Windows и когда сценарий лучше ручной работы.</t>
+          <t xml:space="preserve">Ставите и удаляете пакеты, затем размечаете новый диск, создаёте файловую систему и монтируете её. Сдаёте отчёт с командами, выводом и записью в fstab.</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">оболочка, PowerShell, Bash, параметры команды, автоматизация</t>
+          <t xml:space="preserve">apt, раздел, mkfs, mount, fstab</t>
         </is>
       </c>
     </row>
     <row r="22" ht="60" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">19-20</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 7. Работа с командной строкой Windows; Права доступа и общие папки Windows</t>
+          <t xml:space="preserve">Лекция 11. Службы и автозагрузка</t>
         </is>
       </c>
       <c r="D22" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Работаете в командной строке Windows, затем настраиваете общий каталог и права NTFS для группы. Сдаёте отчёт с командами, списком разрешений и проверкой доступа.</t>
+          <t xml:space="preserve">Служба запускается без входа пользователя и работает в фоне по расписанию или событию. Разберём типы запуска, зависимости и точки автозагрузки в Linux и Windows.</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">cmd, icacls, общий ресурс, разрешения NTFS, сетевая папка</t>
+          <t xml:space="preserve">systemd, демон, тип запуска, зависимости службы, автозагрузка</t>
         </is>
       </c>
     </row>
@@ -692,12 +692,12 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 11. Службы и автозагрузка</t>
+          <t xml:space="preserve">Практика 7. Службы и планировщик Windows</t>
         </is>
       </c>
       <c r="D23" s="6">
@@ -705,16 +705,16 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Служба запускается без входа пользователя и работает в фоне по расписанию или событию. Разберём типы запуска, зависимости и точки автозагрузки в Linux и Windows.</t>
+          <t xml:space="preserve">Создаёте службу и задание в планировщике Windows, проверяете запуск по расписанию и по событию. Сдаёте отчёт с настройками, журналом и разбором сбоя.</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">systemd, демон, тип запуска, зависимости службы, автозагрузка</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="60" customHeight="1">
+          <t xml:space="preserve">sc.exe, планировщик заданий, триггер, учётная запись службы, журнал</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="45" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">22</t>
@@ -722,12 +722,12 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 8. Службы и планировщик Windows</t>
+          <t xml:space="preserve">Лекция 12. Виртуализация: VirtualBox, Linux и Windows 10</t>
         </is>
       </c>
       <c r="D24" s="6">
@@ -735,49 +735,49 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Создаёте службу и задание в планировщике Windows, проверяете запуск по расписанию и по событию. Сдаёте отчёт с настройками, журналом и разбором сбоя.</t>
+          <t xml:space="preserve">Гипервизор делит ресурсы хоста между гостевыми системами, а его тип определяет скорость и изоляцию. Разберём режимы сети VirtualBox и общие папки.</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">sc.exe, планировщик заданий, триггер, учётная запись службы, журнал</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="45" customHeight="1">
+          <t xml:space="preserve">гипервизор, гостевая система, NAT, сетевой мост, снимок</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="60" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">23-24</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 12. Виртуализация: VirtualBox, Linux и Windows 10</t>
+          <t xml:space="preserve">Практика 8. Установка VirtualBox и создание виртуальной машины; Установка Linux в VirtualBox</t>
         </is>
       </c>
       <c r="D25" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Гипервизор делит ресурсы хоста между гостевыми системами, а его тип определяет скорость и изоляцию. Разберём режимы сети VirtualBox и общие папки.</t>
+          <t xml:space="preserve">Создаёте виртуальную машину в VirtualBox, ставите Linux и настраиваете сеть и общие папки. Сдаёте отчёт со скриншотами установки и проверкой загрузки системы.</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">гипервизор, гостевая система, NAT, сетевой мост, снимок</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="45" customHeight="1">
+          <t xml:space="preserve">VirtualBox, виртуальный диск, ISO-образ, установка Linux, сетевой адаптер</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="60" customHeight="1">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 9. Диагностика сети в ОС</t>
+          <t xml:space="preserve">Практика 9. Установка Windows 10 в VirtualBox</t>
         </is>
       </c>
       <c r="D26" s="6">
@@ -795,102 +795,102 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ставите Windows 10 во вторую виртуальную машину, разбиваете диск и завершаете первичную настройку. Сдаёте отчёт с параметрами машины и скриншотами ключевых шагов.</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Windows 10, разметка диска, установка, драйверы, учётная запись</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="45" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Практика</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Практика 10. Монтирование и общие папки VirtualBox</t>
+        </is>
+      </c>
+      <c r="D27" s="6">
+        <v>2</v>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Подключаете общую папку хоста в гостевую систему и проверяете права доступа к ней. Сдаёте отчёт с командами монтирования и проверкой обмена файлами.</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">общая папка, монтирование, vboxsf, права доступа, гостевая система</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Лекция</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Лекция 13. Диагностика, журналы и восстановление ОС</t>
+        </is>
+      </c>
+      <c r="D28" s="6">
+        <v>2</v>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Сбой оставляет следы в журналах, а восстановление начинается с резервной копии и точки возврата. Разберём порядок диагностики от симптома к причине.</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">журнал событий, уровень сообщения, точка восстановления, загрузочный образ, резервная копия</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="45" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Практика</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Практика 11. Диагностика сети в ОС</t>
+        </is>
+      </c>
+      <c r="D29" s="6">
+        <v>2</v>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Проверяете сеть виртуальной машины по шагам: адрес, шлюз, DNS и доступность узла. Сдаёте протокол диагностики с найденной причиной сбоя.</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">ip-адрес, шлюз, DNS, ping, traceroute</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="60" customHeight="1">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Лекция</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Лекция 13. Диагностика, журналы и восстановление ОС</t>
-        </is>
-      </c>
-      <c r="D27" s="6">
-        <v>2</v>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Сбой оставляет следы в журналах, а восстановление начинается с резервной копии и точки возврата. Разберём порядок диагностики от симптома к причине.</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">журнал событий, уровень сообщения, точка восстановления, загрузочный образ, резервная копия</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="45" customHeight="1">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Практика</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Практика 10. Журналы событий и поиск ошибок</t>
-        </is>
-      </c>
-      <c r="D28" s="6">
-        <v>2</v>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ищете причину сбоя по журналам Linux и Windows: фильтруете события, сопоставляете время и находите первую ошибку. Сдаёте разбор с цепочкой событий.</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">journalctl, просмотр событий, фильтр, идентификатор события, время сбоя</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27-28</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Практика</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Практика 11. Управление пакетами Linux; Диски, разделы и файловые системы</t>
-        </is>
-      </c>
-      <c r="D29" s="6">
-        <v>4</v>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ставите и удаляете пакеты, затем размечаете новый диск, создаёте файловую систему и монтируете её. Сдаёте отчёт с командами, выводом и записью в fstab.</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">apt, раздел, mkfs, mount, fstab</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 12. Монтирование и общие папки VirtualBox</t>
+          <t xml:space="preserve">Практика 12. Журналы событий и поиск ошибок</t>
         </is>
       </c>
       <c r="D30" s="6">
@@ -915,12 +915,12 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Подключаете общую папку хоста в гостевую систему и проверяете права доступа к ней. Сдаёте отчёт с командами монтирования и проверкой обмена файлами.</t>
+          <t xml:space="preserve">Ищете причину сбоя по журналам Linux и Windows: фильтруете события, сопоставляете время и находите первую ошибку. Сдаёте разбор с цепочкой событий.</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">общая папка, монтирование, vboxsf, права доступа, гостевая система</t>
+          <t xml:space="preserve">journalctl, просмотр событий, фильтр, идентификатор события, время сбоя</t>
         </is>
       </c>
     </row>
